--- a/database/event/3883/event_3883_evp_summary.xlsx
+++ b/database/event/3883/event_3883_evp_summary.xlsx
@@ -492,35 +492,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9723</v>
+        <v>7.9439</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5404</v>
+        <v>4.0338</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3953</v>
+        <v>2.7209</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9723</v>
+        <v>7.9439</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9047</v>
+        <v>2.9049</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0676</v>
+        <v>5.039</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9047</v>
+        <v>2.9049</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9047</v>
+        <v>2.9049</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0676</v>
+        <v>5.039</v>
       </c>
       <c r="K2" t="n">
         <v>117</v>
@@ -529,7 +529,7 @@
         <v>148</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9723</v>
+        <v>7.943899999999999</v>
       </c>
       <c r="N2" t="n">
         <v>265</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9553</v>
+        <v>7.886</v>
       </c>
       <c r="C3" t="n">
-        <v>3.5318</v>
+        <v>4.0044</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3884</v>
+        <v>2.6979</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9553</v>
+        <v>7.886</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2246</v>
+        <v>2.1553</v>
       </c>
       <c r="G3" t="n">
         <v>5.7307</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2246</v>
+        <v>2.1553</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2246</v>
+        <v>2.1553</v>
       </c>
       <c r="J3" t="n">
         <v>5.7307</v>
@@ -575,7 +575,7 @@
         <v>148</v>
       </c>
       <c r="M3" t="n">
-        <v>6.955299999999999</v>
+        <v>7.885999999999999</v>
       </c>
       <c r="N3" t="n">
         <v>265</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6027</v>
+        <v>7.4606</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3527</v>
+        <v>3.7884</v>
       </c>
       <c r="D4" t="n">
-        <v>2.246</v>
+        <v>2.5284</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6027</v>
+        <v>7.4606</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5637</v>
+        <v>3.4656</v>
       </c>
       <c r="G4" t="n">
-        <v>5.039</v>
+        <v>3.995</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5637</v>
+        <v>3.4656</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5637</v>
+        <v>3.4656</v>
       </c>
       <c r="J4" t="n">
-        <v>5.039</v>
+        <v>3.995</v>
       </c>
       <c r="K4" t="n">
         <v>117</v>
@@ -621,7 +621,7 @@
         <v>148</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6027</v>
+        <v>7.460599999999999</v>
       </c>
       <c r="N4" t="n">
         <v>265</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.5666</v>
+        <v>6.9955</v>
       </c>
       <c r="C5" t="n">
-        <v>3.3344</v>
+        <v>3.5522</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2314</v>
+        <v>2.3431</v>
       </c>
       <c r="E5" t="n">
-        <v>6.5666</v>
+        <v>6.9955</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5716</v>
+        <v>1.9279</v>
       </c>
       <c r="G5" t="n">
-        <v>3.995</v>
+        <v>5.0676</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5716</v>
+        <v>1.9279</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5716</v>
+        <v>1.9279</v>
       </c>
       <c r="J5" t="n">
-        <v>3.995</v>
+        <v>5.0676</v>
       </c>
       <c r="K5" t="n">
         <v>117</v>
@@ -667,7 +667,7 @@
         <v>148</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5666</v>
+        <v>6.9955</v>
       </c>
       <c r="N5" t="n">
         <v>265</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.9373</v>
+        <v>6.3314</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0149</v>
+        <v>3.215</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9772</v>
+        <v>2.0785</v>
       </c>
       <c r="E6" t="n">
-        <v>5.9373</v>
+        <v>6.3314</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0234</v>
+        <v>4.4175</v>
       </c>
       <c r="G6" t="n">
         <v>1.9139</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0234</v>
+        <v>4.6236</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0234</v>
+        <v>4.6236</v>
       </c>
       <c r="J6" t="n">
         <v>1.9139</v>
@@ -713,7 +713,7 @@
         <v>131</v>
       </c>
       <c r="M6" t="n">
-        <v>5.9373</v>
+        <v>6.5375</v>
       </c>
       <c r="N6" t="n">
         <v>305</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6953</v>
+        <v>5.5296</v>
       </c>
       <c r="C7" t="n">
-        <v>2.3842</v>
+        <v>2.8078</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4754</v>
+        <v>1.7591</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6953</v>
+        <v>5.5296</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3599</v>
+        <v>4.1942</v>
       </c>
       <c r="G7" t="n">
         <v>1.3354</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3599</v>
+        <v>4.2734</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3599</v>
+        <v>4.2734</v>
       </c>
       <c r="J7" t="n">
         <v>1.3354</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>4.6953</v>
+        <v>5.6088</v>
       </c>
       <c r="N7" t="n">
         <v>227</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.1479</v>
+        <v>4.3825</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1062</v>
+        <v>2.2254</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2543</v>
+        <v>1.3021</v>
       </c>
       <c r="E8" t="n">
-        <v>4.1479</v>
+        <v>4.3825</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4374</v>
+        <v>2.672</v>
       </c>
       <c r="G8" t="n">
         <v>1.7105</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4374</v>
+        <v>2.672</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4374</v>
+        <v>2.672</v>
       </c>
       <c r="J8" t="n">
         <v>1.7105</v>
@@ -805,7 +805,7 @@
         <v>131</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1479</v>
+        <v>4.3825</v>
       </c>
       <c r="N8" t="n">
         <v>305</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8544</v>
+        <v>4.0856</v>
       </c>
       <c r="C9" t="n">
-        <v>1.9572</v>
+        <v>2.0746</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1357</v>
+        <v>1.1838</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8544</v>
+        <v>4.0856</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6803</v>
+        <v>1.9115</v>
       </c>
       <c r="G9" t="n">
         <v>2.1741</v>
       </c>
       <c r="H9" t="n">
-        <v>1.6803</v>
+        <v>1.9115</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6803</v>
+        <v>1.9115</v>
       </c>
       <c r="J9" t="n">
         <v>2.1741</v>
@@ -851,7 +851,7 @@
         <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8544</v>
+        <v>4.0856</v>
       </c>
       <c r="N9" t="n">
         <v>305</v>
@@ -860,320 +860,320 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6441</v>
+        <v>3.8394</v>
       </c>
       <c r="C10" t="n">
-        <v>1.8504</v>
+        <v>1.9496</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0508</v>
+        <v>1.0857</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6441</v>
+        <v>3.8394</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9034</v>
+        <v>4.5132</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7406</v>
+        <v>-0.6738</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9034</v>
+        <v>4.7737</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9034</v>
+        <v>4.8138</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7406</v>
+        <v>-0.6738</v>
       </c>
       <c r="K10" t="n">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="L10" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>3.644</v>
+        <v>4.14</v>
       </c>
       <c r="N10" t="n">
-        <v>227</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6301</v>
+        <v>3.6544</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8433</v>
+        <v>1.8556</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0451</v>
+        <v>1.012</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6301</v>
+        <v>3.6544</v>
       </c>
       <c r="F11" t="n">
-        <v>1.848</v>
+        <v>3.652</v>
       </c>
       <c r="G11" t="n">
-        <v>1.7821</v>
+        <v>0.0024</v>
       </c>
       <c r="H11" t="n">
-        <v>1.848</v>
+        <v>3.652</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8653</v>
+        <v>3.652</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7821</v>
+        <v>0.0024</v>
       </c>
       <c r="K11" t="n">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="L11" t="n">
-        <v>188</v>
+        <v>48</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6474</v>
+        <v>3.6544</v>
       </c>
       <c r="N11" t="n">
-        <v>435</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4891</v>
+        <v>3.6441</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7717</v>
+        <v>1.8504</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9882</v>
+        <v>1.0079</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4891</v>
+        <v>3.6441</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1629</v>
+        <v>0.9034</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6738</v>
+        <v>2.7406</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2244</v>
+        <v>0.9034</v>
       </c>
       <c r="I12" t="n">
-        <v>4.244</v>
+        <v>0.9034</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6738</v>
+        <v>2.7406</v>
       </c>
       <c r="K12" t="n">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5702</v>
+        <v>3.644</v>
       </c>
       <c r="N12" t="n">
-        <v>267</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.0103</v>
+        <v>3.6164</v>
       </c>
       <c r="C13" t="n">
-        <v>1.5286</v>
+        <v>1.8363</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7947</v>
+        <v>0.9969</v>
       </c>
       <c r="E13" t="n">
-        <v>3.0103</v>
+        <v>3.6164</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0103</v>
+        <v>1.8343</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.7821</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0103</v>
+        <v>1.8343</v>
       </c>
       <c r="I13" t="n">
-        <v>3.0103</v>
+        <v>1.8653</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1.7821</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0103</v>
+        <v>3.6474</v>
       </c>
       <c r="N13" t="n">
-        <v>204</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8932</v>
+        <v>3.0728</v>
       </c>
       <c r="C14" t="n">
-        <v>1.4691</v>
+        <v>1.5603</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7474</v>
+        <v>0.7803</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8932</v>
+        <v>3.0728</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6658</v>
+        <v>3.0728</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2274</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6658</v>
+        <v>3.0728</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6906</v>
+        <v>3.0728</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2274</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="L14" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.918</v>
+        <v>3.0728</v>
       </c>
       <c r="N14" t="n">
-        <v>435</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.7435</v>
+        <v>3.0103</v>
       </c>
       <c r="C15" t="n">
-        <v>1.3931</v>
+        <v>1.5286</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.7554</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7435</v>
+        <v>3.0103</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6336</v>
+        <v>3.0103</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1099</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6336</v>
+        <v>3.0103</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6458</v>
+        <v>3.0103</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1099</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7557</v>
+        <v>3.0103</v>
       </c>
       <c r="N15" t="n">
-        <v>264</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3507</v>
+        <v>2.973</v>
       </c>
       <c r="C16" t="n">
-        <v>1.1936</v>
+        <v>1.5096</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5283</v>
+        <v>0.7405</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3507</v>
+        <v>2.973</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3483</v>
+        <v>2.973</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3483</v>
+        <v>2.973</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3483</v>
+        <v>2.973</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>202</v>
+        <v>250</v>
       </c>
       <c r="L16" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.3507</v>
+        <v>2.973</v>
       </c>
       <c r="N16" t="n">
         <v>250</v>
@@ -1182,47 +1182,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.3398</v>
+        <v>2.8733</v>
       </c>
       <c r="C17" t="n">
-        <v>1.1881</v>
+        <v>1.459</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5239</v>
+        <v>0.7008</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3398</v>
+        <v>2.8733</v>
       </c>
       <c r="F17" t="n">
-        <v>2.264</v>
+        <v>2.6459</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2274</v>
       </c>
       <c r="H17" t="n">
-        <v>2.264</v>
+        <v>2.6459</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2746</v>
+        <v>2.6906</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.2274</v>
       </c>
       <c r="K17" t="n">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="L17" t="n">
-        <v>52</v>
+        <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>2.3504</v>
+        <v>2.918</v>
       </c>
       <c r="N17" t="n">
-        <v>267</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="C18" t="n">
-        <v>1.1483</v>
+        <v>1.4297</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4922</v>
+        <v>0.6778</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.2613</v>
+        <v>2.8156</v>
       </c>
       <c r="N18" t="n">
         <v>172</v>
@@ -1274,139 +1274,139 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.2454</v>
+        <v>2.7337</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1402</v>
+        <v>1.3881</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4857</v>
+        <v>0.6452</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2454</v>
+        <v>2.7337</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2454</v>
+        <v>2.6238</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.1099</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2454</v>
+        <v>2.6238</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2454</v>
+        <v>2.6458</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.1099</v>
       </c>
       <c r="K19" t="n">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2454</v>
+        <v>2.7557</v>
       </c>
       <c r="N19" t="n">
-        <v>186</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="C20" t="n">
-        <v>1.0956</v>
+        <v>1.2849</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4503</v>
+        <v>0.5642</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1577</v>
+        <v>2.5304</v>
       </c>
       <c r="N20" t="n">
-        <v>250</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.1354</v>
+        <v>2.3421</v>
       </c>
       <c r="C21" t="n">
-        <v>1.0843</v>
+        <v>1.1893</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4413</v>
+        <v>0.4892</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1354</v>
+        <v>2.3421</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1354</v>
+        <v>2.2663</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.1354</v>
+        <v>2.2663</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1354</v>
+        <v>2.2853</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M21" t="n">
-        <v>2.1354</v>
+        <v>2.3611</v>
       </c>
       <c r="N21" t="n">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="C22" t="n">
-        <v>1.0624</v>
+        <v>1.1509</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4238</v>
+        <v>0.4591</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="F22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.0922</v>
+        <v>2.2665</v>
       </c>
       <c r="N22" t="n">
         <v>172</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.8612</v>
+        <v>2.133</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9451000000000001</v>
+        <v>1.0831</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3305</v>
+        <v>0.4059</v>
       </c>
       <c r="E23" t="n">
-        <v>1.8612</v>
+        <v>2.133</v>
       </c>
       <c r="F23" t="n">
-        <v>1.9947</v>
+        <v>2.2665</v>
       </c>
       <c r="G23" t="n">
         <v>-0.1335</v>
       </c>
       <c r="H23" t="n">
-        <v>1.9947</v>
+        <v>2.2665</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9947</v>
+        <v>2.2665</v>
       </c>
       <c r="J23" t="n">
         <v>-0.1335</v>
@@ -1495,7 +1495,7 @@
         <v>62</v>
       </c>
       <c r="M23" t="n">
-        <v>1.8612</v>
+        <v>2.133</v>
       </c>
       <c r="N23" t="n">
         <v>174</v>
@@ -1504,357 +1504,357 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6686</v>
+        <v>1.8522</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.9405</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2527</v>
+        <v>0.294</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6686</v>
+        <v>1.8522</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1734</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4952</v>
+        <v>1.2217</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1734</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1843</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4952</v>
+        <v>1.2217</v>
       </c>
       <c r="K24" t="n">
-        <v>247</v>
+        <v>174</v>
       </c>
       <c r="L24" t="n">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6795</v>
+        <v>1.8522</v>
       </c>
       <c r="N24" t="n">
-        <v>435</v>
+        <v>305</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.5263</v>
+        <v>1.7717</v>
       </c>
       <c r="C25" t="n">
-        <v>0.775</v>
+        <v>0.8996</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1952</v>
+        <v>0.2619</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5263</v>
+        <v>1.7717</v>
       </c>
       <c r="F25" t="n">
-        <v>1.5263</v>
+        <v>1.8426</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.0709</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5263</v>
+        <v>1.8426</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5263</v>
+        <v>1.8581</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.0709</v>
       </c>
       <c r="K25" t="n">
-        <v>133</v>
+        <v>214</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M25" t="n">
-        <v>1.5263</v>
+        <v>1.7872</v>
       </c>
       <c r="N25" t="n">
-        <v>133</v>
+        <v>264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.504</v>
+        <v>1.6598</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7637</v>
+        <v>0.8428</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1862</v>
+        <v>0.2174</v>
       </c>
       <c r="E26" t="n">
-        <v>1.504</v>
+        <v>1.6598</v>
       </c>
       <c r="F26" t="n">
-        <v>2.0059</v>
+        <v>1.1646</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5019</v>
+        <v>0.4952</v>
       </c>
       <c r="H26" t="n">
-        <v>2.0059</v>
+        <v>1.1646</v>
       </c>
       <c r="I26" t="n">
-        <v>2.0059</v>
+        <v>1.1843</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5019</v>
+        <v>0.4952</v>
       </c>
       <c r="K26" t="n">
-        <v>202</v>
+        <v>247</v>
       </c>
       <c r="L26" t="n">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="M26" t="n">
-        <v>1.504</v>
+        <v>1.6795</v>
       </c>
       <c r="N26" t="n">
-        <v>250</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.4111</v>
+        <v>1.6452</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7165</v>
+        <v>0.8354</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1487</v>
+        <v>0.2115</v>
       </c>
       <c r="E27" t="n">
-        <v>1.4111</v>
+        <v>1.6452</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4111</v>
+        <v>1.8943</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.2491</v>
       </c>
       <c r="H27" t="n">
-        <v>1.4111</v>
+        <v>1.8943</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4111</v>
+        <v>1.8943</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.2491</v>
       </c>
       <c r="K27" t="n">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M27" t="n">
-        <v>1.4111</v>
+        <v>1.6452</v>
       </c>
       <c r="N27" t="n">
-        <v>135</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.3957</v>
+        <v>1.5812</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7087</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1425</v>
+        <v>0.186</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3957</v>
+        <v>1.5812</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1857</v>
+        <v>2.284</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.79</v>
+        <v>-0.7028</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1857</v>
+        <v>2.284</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1959</v>
+        <v>2.284</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.79</v>
+        <v>-0.7028</v>
       </c>
       <c r="K28" t="n">
-        <v>215</v>
+        <v>112</v>
       </c>
       <c r="L28" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="M28" t="n">
-        <v>1.4059</v>
+        <v>1.5812</v>
       </c>
       <c r="N28" t="n">
-        <v>267</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.3214</v>
+        <v>1.5263</v>
       </c>
       <c r="C29" t="n">
-        <v>0.671</v>
+        <v>0.775</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1125</v>
+        <v>0.1642</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3214</v>
+        <v>1.5263</v>
       </c>
       <c r="F29" t="n">
-        <v>1.3923</v>
+        <v>1.5263</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0709</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.3923</v>
+        <v>1.5263</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3988</v>
+        <v>1.5263</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0709</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.3279</v>
+        <v>1.5263</v>
       </c>
       <c r="N29" t="n">
-        <v>264</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2222</v>
+        <v>1.5162</v>
       </c>
       <c r="C30" t="n">
-        <v>0.6206</v>
+        <v>0.7699</v>
       </c>
       <c r="D30" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.1601</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2222</v>
+        <v>1.5162</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0005</v>
+        <v>1.5162</v>
       </c>
       <c r="G30" t="n">
-        <v>1.2217</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0005</v>
+        <v>1.5162</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0005</v>
+        <v>1.5162</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2217</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="L30" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2222</v>
+        <v>1.5162</v>
       </c>
       <c r="N30" t="n">
-        <v>305</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.1656</v>
+        <v>1.504</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5919</v>
+        <v>0.7637</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0495</v>
+        <v>0.1553</v>
       </c>
       <c r="E31" t="n">
-        <v>1.1656</v>
+        <v>1.504</v>
       </c>
       <c r="F31" t="n">
-        <v>1.4147</v>
+        <v>2.0059</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2491</v>
+        <v>-0.5019</v>
       </c>
       <c r="H31" t="n">
-        <v>1.4147</v>
+        <v>2.0059</v>
       </c>
       <c r="I31" t="n">
-        <v>1.4147</v>
+        <v>2.0059</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2491</v>
+        <v>-0.5019</v>
       </c>
       <c r="K31" t="n">
         <v>202</v>
@@ -1863,7 +1863,7 @@
         <v>48</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1656</v>
+        <v>1.504</v>
       </c>
       <c r="N31" t="n">
         <v>250</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1062</v>
+        <v>1.4632</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5617</v>
+        <v>0.743</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0255</v>
+        <v>0.139</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1062</v>
+        <v>1.4632</v>
       </c>
       <c r="F32" t="n">
-        <v>2.6298</v>
+        <v>2.9868</v>
       </c>
       <c r="G32" t="n">
         <v>-1.5236</v>
       </c>
       <c r="H32" t="n">
-        <v>2.6298</v>
+        <v>2.9868</v>
       </c>
       <c r="I32" t="n">
-        <v>2.6298</v>
+        <v>2.9868</v>
       </c>
       <c r="J32" t="n">
         <v>-1.5236</v>
@@ -1909,7 +1909,7 @@
         <v>148</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1062</v>
+        <v>1.4632</v>
       </c>
       <c r="N32" t="n">
         <v>265</v>
@@ -1918,93 +1918,93 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.0853</v>
+        <v>1.4111</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5511</v>
+        <v>0.7165</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0171</v>
+        <v>0.1183</v>
       </c>
       <c r="E33" t="n">
-        <v>1.0853</v>
+        <v>1.4111</v>
       </c>
       <c r="F33" t="n">
-        <v>1.0728</v>
+        <v>1.4111</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0125</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.0728</v>
+        <v>1.4111</v>
       </c>
       <c r="I33" t="n">
-        <v>1.0728</v>
+        <v>1.4111</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0125</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="L33" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.0853</v>
+        <v>1.4111</v>
       </c>
       <c r="N33" t="n">
-        <v>174</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.0455</v>
+        <v>1.3877</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5309</v>
+        <v>0.7047</v>
       </c>
       <c r="D34" t="n">
-        <v>0.001</v>
+        <v>0.1089</v>
       </c>
       <c r="E34" t="n">
-        <v>1.0455</v>
+        <v>1.3877</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7483</v>
+        <v>2.1777</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.7028</v>
+        <v>-0.79</v>
       </c>
       <c r="H34" t="n">
-        <v>1.7483</v>
+        <v>2.1777</v>
       </c>
       <c r="I34" t="n">
-        <v>1.7483</v>
+        <v>2.196</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.7028</v>
+        <v>-0.79</v>
       </c>
       <c r="K34" t="n">
-        <v>112</v>
+        <v>215</v>
       </c>
       <c r="L34" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M34" t="n">
-        <v>1.0455</v>
+        <v>1.406</v>
       </c>
       <c r="N34" t="n">
-        <v>174</v>
+        <v>267</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5258</v>
+        <v>0.6479</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0031</v>
+        <v>0.0644</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0354</v>
+        <v>1.2759</v>
       </c>
       <c r="N35" t="n">
         <v>172</v>
@@ -2056,47 +2056,47 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7935</v>
+        <v>1.0853</v>
       </c>
       <c r="C36" t="n">
-        <v>0.4029</v>
+        <v>0.5511</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.1008</v>
+        <v>-0.0115</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7935</v>
+        <v>1.0853</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7935</v>
+        <v>1.0728</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7935</v>
+        <v>1.0728</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7935</v>
+        <v>1.0728</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="K36" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7935</v>
+        <v>1.0853</v>
       </c>
       <c r="N36" t="n">
-        <v>121</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37">
@@ -2112,7 +2112,7 @@
         <v>0.3801</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1189</v>
+        <v>-0.1457</v>
       </c>
       <c r="E37" t="n">
         <v>0.7486</v>
@@ -2148,461 +2148,461 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6965</v>
       </c>
       <c r="C38" t="n">
-        <v>0.3084</v>
+        <v>0.3537</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.176</v>
+        <v>-0.1664</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.6965</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4323</v>
+        <v>1.019</v>
       </c>
       <c r="G38" t="n">
-        <v>1.0397</v>
+        <v>-0.3225</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4323</v>
+        <v>1.019</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4323</v>
+        <v>1.0276</v>
       </c>
       <c r="J38" t="n">
-        <v>1.0397</v>
+        <v>-0.3225</v>
       </c>
       <c r="K38" t="n">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="L38" t="n">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.7051000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>227</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6057</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="C39" t="n">
-        <v>0.3076</v>
+        <v>0.3084</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1767</v>
+        <v>-0.2019</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6057</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6057</v>
+        <v>-0.4323</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1.0397</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6057</v>
+        <v>-0.4323</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6057</v>
+        <v>-0.4323</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1.0397</v>
       </c>
       <c r="K39" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6057</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>135</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6008</v>
+        <v>0.6057</v>
       </c>
       <c r="C40" t="n">
-        <v>0.3051</v>
+        <v>0.3076</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.1787</v>
+        <v>-0.2026</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6008</v>
+        <v>0.6057</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9233</v>
+        <v>0.6057</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9233</v>
+        <v>0.6057</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9276</v>
+        <v>0.6057</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.3225</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="L40" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6051</v>
+        <v>0.6057</v>
       </c>
       <c r="N40" t="n">
-        <v>267</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2543</v>
+        <v>0.3011</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2191</v>
+        <v>-0.2077</v>
       </c>
       <c r="E41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="I41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>186</v>
+        <v>121</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.5008</v>
+        <v>0.593</v>
       </c>
       <c r="N41" t="n">
-        <v>186</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3481</v>
+        <v>0.5319</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1768</v>
+        <v>0.2701</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2807</v>
+        <v>-0.232</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3481</v>
+        <v>0.5319</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0464</v>
+        <v>0.5319</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.6983</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0464</v>
+        <v>0.5319</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0464</v>
+        <v>0.5319</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.6983</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>112</v>
+        <v>186</v>
       </c>
       <c r="L42" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3481</v>
+        <v>0.5319</v>
       </c>
       <c r="N42" t="n">
-        <v>174</v>
+        <v>186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3028</v>
+        <v>0.5245</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1538</v>
+        <v>0.2663</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.299</v>
+        <v>-0.2349</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3028</v>
+        <v>0.5245</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3028</v>
+        <v>1.2228</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.6983</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3028</v>
+        <v>1.2228</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3028</v>
+        <v>1.2228</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.6983</v>
       </c>
       <c r="K43" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3028</v>
+        <v>0.5245000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1385</v>
+        <v>0.2052</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.3112</v>
+        <v>-0.2829</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2728</v>
+        <v>0.4042</v>
       </c>
       <c r="N44" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1136</v>
+        <v>0.2036</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.331</v>
+        <v>-0.2842</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2238</v>
+        <v>0.4009</v>
       </c>
       <c r="N45" t="n">
-        <v>204</v>
+        <v>172</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="C46" t="n">
-        <v>0.112</v>
+        <v>0.1136</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3323</v>
+        <v>-0.3547</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.2205</v>
+        <v>0.2238</v>
       </c>
       <c r="N46" t="n">
-        <v>133</v>
+        <v>204</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1073</v>
+        <v>0.112</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.336</v>
+        <v>-0.3561</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="F47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.2113</v>
+        <v>0.2205</v>
       </c>
       <c r="N47" t="n">
-        <v>172</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48">
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.1645</v>
+        <v>0.1787</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0835</v>
+        <v>0.0907</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3549</v>
+        <v>-0.3727</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1645</v>
+        <v>0.1787</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.916</v>
+        <v>-1.9018</v>
       </c>
       <c r="G48" t="n">
         <v>2.0805</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.916</v>
+        <v>-1.9018</v>
       </c>
       <c r="I48" t="n">
         <v>-1.9339</v>
@@ -2664,7 +2664,7 @@
         <v>-0.0019</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4229</v>
+        <v>-0.4454</v>
       </c>
       <c r="E49" t="n">
         <v>-0.0037</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0251</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4414</v>
+        <v>-0.4636</v>
       </c>
       <c r="E50" t="n">
         <v>-0.0495</v>
@@ -2756,7 +2756,7 @@
         <v>-0.1106</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5093</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E51" t="n">
         <v>-0.2178</v>
@@ -2802,7 +2802,7 @@
         <v>-0.1205</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.5173</v>
+        <v>-0.5385</v>
       </c>
       <c r="E52" t="n">
         <v>-0.2374</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1464</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5379</v>
+        <v>-0.5588</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2884</v>
@@ -2894,7 +2894,7 @@
         <v>-0.183</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5669</v>
+        <v>-0.5875</v>
       </c>
       <c r="E54" t="n">
         <v>-0.3603</v>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5804</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2951</v>
+        <v>-0.2947</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6561</v>
+        <v>-0.6751</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5810999999999999</v>
+        <v>-0.5804</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.1802</v>
+        <v>-0.1795</v>
       </c>
       <c r="G55" t="n">
         <v>-0.4009</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.1802</v>
+        <v>-0.1795</v>
       </c>
       <c r="I55" t="n">
         <v>-0.181</v>
@@ -2986,7 +2986,7 @@
         <v>-0.2963</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6571</v>
+        <v>-0.6764</v>
       </c>
       <c r="E56" t="n">
         <v>-0.5836</v>
@@ -3022,323 +3022,323 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.6398</v>
+        <v>-0.6011</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.3249</v>
+        <v>-0.3052</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6798</v>
+        <v>-0.6834</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.6398</v>
+        <v>-0.6011</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.6398</v>
+        <v>-0.8403</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>0.2392</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.6398</v>
+        <v>-0.8403</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.6398</v>
+        <v>-0.8403</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.2392</v>
       </c>
       <c r="K57" t="n">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.6398</v>
+        <v>-0.6011000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>142</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.3384</v>
+        <v>-0.3249</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6906</v>
+        <v>-0.6988</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.6665</v>
+        <v>-0.6398</v>
       </c>
       <c r="N58" t="n">
-        <v>204</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6852</v>
+        <v>-0.6665</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.3479</v>
+        <v>-0.3384</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6982</v>
+        <v>-0.7094</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6852</v>
+        <v>-0.6665</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3148</v>
+        <v>-0.6665</v>
       </c>
       <c r="G59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3148</v>
+        <v>-0.6665</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3148</v>
+        <v>-0.6665</v>
       </c>
       <c r="J59" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L59" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6852</v>
+        <v>-0.6665</v>
       </c>
       <c r="N59" t="n">
-        <v>250</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6948</v>
+        <v>-0.6846</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.3528</v>
+        <v>-0.3476</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.702</v>
+        <v>-0.7167</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6948</v>
+        <v>-0.6846</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.1862</v>
+        <v>-1</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.1862</v>
+        <v>-1</v>
       </c>
       <c r="K60" t="n">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="L60" t="n">
-        <v>131</v>
+        <v>48</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6948000000000001</v>
+        <v>-0.6846</v>
       </c>
       <c r="N60" t="n">
-        <v>305</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.7312</v>
+        <v>-0.6948</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3713</v>
+        <v>-0.3528</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7168</v>
+        <v>-0.7207</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.7312</v>
+        <v>-0.6948</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.7312</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>-0.1862</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.7312</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7312</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>-0.1862</v>
       </c>
       <c r="K61" t="n">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.7312</v>
+        <v>-0.6948000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>204</v>
+        <v>305</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7518</v>
+        <v>-0.7312</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.3818</v>
+        <v>-0.3713</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7251</v>
+        <v>-0.7352</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7518</v>
+        <v>-0.7312</v>
       </c>
       <c r="F62" t="n">
-        <v>0.206</v>
+        <v>-0.7312</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.9578</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.206</v>
+        <v>-0.7312</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2079</v>
+        <v>-0.7312</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.9578</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="L62" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7499</v>
+        <v>-0.7312</v>
       </c>
       <c r="N62" t="n">
-        <v>435</v>
+        <v>204</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.7628</v>
+        <v>-0.7533</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3873</v>
+        <v>-0.3825</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7295</v>
+        <v>-0.744</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.7628</v>
+        <v>-0.7533</v>
       </c>
       <c r="F63" t="n">
-        <v>-1.002</v>
+        <v>0.2045</v>
       </c>
       <c r="G63" t="n">
-        <v>0.2392</v>
+        <v>-0.9578</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.002</v>
+        <v>0.2045</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.002</v>
+        <v>0.2079</v>
       </c>
       <c r="J63" t="n">
-        <v>0.2392</v>
+        <v>-0.9578</v>
       </c>
       <c r="K63" t="n">
-        <v>124</v>
+        <v>247</v>
       </c>
       <c r="L63" t="n">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.7628</v>
+        <v>-0.7499</v>
       </c>
       <c r="N63" t="n">
-        <v>227</v>
+        <v>435</v>
       </c>
     </row>
     <row r="64">
@@ -3354,7 +3354,7 @@
         <v>-0.3922</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.7516</v>
       </c>
       <c r="E64" t="n">
         <v>-0.7724</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3931</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7341</v>
+        <v>-0.7524</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7742</v>
@@ -3436,228 +3436,228 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4589</v>
+        <v>-0.4434</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7864</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.9036999999999999</v>
+        <v>-0.8732</v>
       </c>
       <c r="N66" t="n">
-        <v>135</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4862</v>
+        <v>-0.4589</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8082</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.9575</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="N67" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.084</v>
+        <v>-0.9575</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5504</v>
+        <v>-0.4862</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8593</v>
+        <v>-0.8254</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.084</v>
+        <v>-0.9575</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.9575</v>
       </c>
       <c r="G68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.9575</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0844</v>
+        <v>-0.9575</v>
       </c>
       <c r="J68" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.0844</v>
+        <v>-0.9575</v>
       </c>
       <c r="N68" t="n">
-        <v>264</v>
+        <v>204</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.1876</v>
+        <v>-0.9716</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.603</v>
+        <v>-0.4934</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9011</v>
+        <v>-0.831</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.1876</v>
+        <v>-0.9716</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.1876</v>
+        <v>0.0284</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.1876</v>
+        <v>0.0284</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.1876</v>
+        <v>0.0286</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K69" t="n">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.1876</v>
+        <v>-0.9714</v>
       </c>
       <c r="N69" t="n">
-        <v>121</v>
+        <v>264</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.363</v>
+        <v>-1.0087</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6921</v>
+        <v>-0.5122</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.972</v>
+        <v>-0.8458</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.363</v>
+        <v>-1.0087</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.363</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.363</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.363</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K70" t="n">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.363</v>
+        <v>-1.0087</v>
       </c>
       <c r="N70" t="n">
         <v>250</v>
@@ -3666,277 +3666,277 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.7000999999999999</v>
+        <v>-0.603</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9784</v>
+        <v>-0.9171</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.3788</v>
+        <v>-1.1876</v>
       </c>
       <c r="N71" t="n">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.707</v>
+        <v>-0.7000999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9838</v>
+        <v>-0.9932</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="G72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="J72" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>202</v>
+        <v>142</v>
       </c>
       <c r="L72" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3923</v>
+        <v>-1.3788</v>
       </c>
       <c r="N72" t="n">
-        <v>250</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ALEX</t>
+          <t>Zellsis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7993</v>
+        <v>-0.7437</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0573</v>
+        <v>-1.0274</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.5741</v>
+        <v>-1.4647</v>
       </c>
       <c r="N73" t="n">
-        <v>250</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>ALEX</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8068</v>
+        <v>-0.7993</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0632</v>
+        <v>-1.071</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>121</v>
+        <v>250</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.5888</v>
+        <v>-1.5741</v>
       </c>
       <c r="N74" t="n">
-        <v>121</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6083</v>
+        <v>-1.5888</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8167</v>
+        <v>-0.8068</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0711</v>
+        <v>-1.0769</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6083</v>
+        <v>-1.5888</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.6083</v>
+        <v>-1.5888</v>
       </c>
       <c r="G75" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.6083</v>
+        <v>-1.5888</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.6111</v>
+        <v>-1.5888</v>
       </c>
       <c r="J75" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>214</v>
+        <v>121</v>
       </c>
       <c r="L75" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.6111</v>
+        <v>-1.5888</v>
       </c>
       <c r="N75" t="n">
-        <v>264</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zellsis</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6243</v>
+        <v>-1.606</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.8248</v>
+        <v>-0.8155</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0775</v>
+        <v>-1.0837</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6243</v>
+        <v>-1.606</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.6243</v>
+        <v>-0.606</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.6243</v>
+        <v>-0.606</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.6243</v>
+        <v>-0.6111</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K76" t="n">
-        <v>172</v>
+        <v>214</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.6243</v>
+        <v>-1.6111</v>
       </c>
       <c r="N76" t="n">
-        <v>172</v>
+        <v>264</v>
       </c>
     </row>
     <row r="77">
@@ -3946,25 +3946,25 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.6375</v>
+        <v>-1.633</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.8315</v>
+        <v>-0.8292</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0829</v>
+        <v>-1.0945</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.6375</v>
+        <v>-1.633</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.219</v>
+        <v>-1.2145</v>
       </c>
       <c r="G77" t="n">
         <v>-0.4185</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.219</v>
+        <v>-1.2145</v>
       </c>
       <c r="I77" t="n">
         <v>-1.2247</v>
@@ -3998,7 +3998,7 @@
         <v>-0.9697</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1928</v>
+        <v>-1.2047</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9097</v>
@@ -4044,7 +4044,7 @@
         <v>-1.0389</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2479</v>
+        <v>-1.259</v>
       </c>
       <c r="E79" t="n">
         <v>-2.046</v>
@@ -4090,7 +4090,7 @@
         <v>-1.1211</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3133</v>
+        <v>-1.3235</v>
       </c>
       <c r="E80" t="n">
         <v>-2.2079</v>
@@ -4136,7 +4136,7 @@
         <v>-1.5211</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6315</v>
+        <v>-1.6373</v>
       </c>
       <c r="E81" t="n">
         <v>-2.9955</v>
